--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_616_Poland.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_616_Poland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5359a6c958924187"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R757da2b428b04c86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1a6f8e1ce140407e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R3f22fb9d8b104a68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Ra005503716df4b63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R4deea51cfaa941f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R18c0c8174e65423c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R11d246e458ee4f9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1bb54733f1ff45f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rff82e6c3988a4acd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Radadf22a08bb4153"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb0f130f5ad3a4e1d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ616CommercialTable" displayName="EEZ616CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ616CommercialTable" displayName="EEZ616CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ616FunctionalTable" displayName="EEZ616FunctionalTable" ref="A1:O15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O15"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ616FunctionalTable" displayName="EEZ616FunctionalTable" ref="A1:E15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E15"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ616ValidationTable" displayName="EEZ616ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ616ValidationTable" displayName="EEZ616ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4446,7 +4400,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06606ad5c07f4eaa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4478170c880493f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4456,20 +4410,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4477,498 +4421,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>16063.5245840874</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.1187050950534525</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1314.3320401681592</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>16063.5245840874</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1343.188362387304</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$57,A2,'Species'!$U$2:$U$57))</x:f>
-        <x:v>21576339.280268554</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.1187050950534525</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1314.3320401681592</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>21112805.038894974</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>463534.24137357995</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0219551234674709</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.021955123467470854</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>14639.332142645899</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4343715821963476</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>271.8764447831204</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>14639.332142645899</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>301.7260907163297</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$57,A3,'Species'!$U$2:$U$57))</x:f>
-        <x:v>4417068.458098457</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4343715821963476</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>271.8764447831204</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3980089.5769418273</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>436978.8811566299</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1097912176872136</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.10979121768721356</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>118924.9043926718</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.16891383782468</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>147.54137884261326</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>118924.9043926718</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>161.49533319003416</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$57,A4,'Species'!$U$2:$U$57))</x:f>
-        <x:v>19205817.059487488</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.16891383782468</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>147.54137884261326</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>17546344.37282075</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1659472.6866667382</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.094576548334322</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.09457654833432187</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.04108159</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.75</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>562.341325190349</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.04108159</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>562.341325190349</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$57,A5,'Species'!$U$2:$U$57))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>23.101875761526593</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.75</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>562.341325190349</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>23.101875761526593</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3181.243504898</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.9416735710971365</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>87.43263579858363</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3181.243504898</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>113.35746368315822</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$57,A6,'Species'!$U$2:$U$57))</x:f>
-        <x:v>360617.695073758</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.9416735710971365</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>87.43263579858363</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>278144.50475035654</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>82473.19032340148</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.296512024918212</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.29651202491821205</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2105.8099043842</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.8952974159126494</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>785.7735681287119</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2105.8099043842</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1344.9944514826175</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$57,A7,'Species'!$U$2:$U$57))</x:f>
-        <x:v>2832302.63727389</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.8952974159126494</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>785.7735681287119</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1654689.7623687543</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1177612.8749051357</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7116819730723034</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.7116819730723033</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>317.2070593749</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7153867483506904</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>519.2622470241637</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>317.2070593749</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>999.7566346284088</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$57,A8,'Species'!$U$2:$U$57))</x:f>
-        <x:v>317129.8621610239</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7153867483506904</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>519.2622470241637</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>164713.65042293788</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>152416.211738086</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.9253405006004327</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.9253405006004327</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.6426861095</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.876266859965487</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>752.0848839925635</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.6426861095</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>755.6542679421893</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$57,A9,'Species'!$U$2:$U$57))</x:f>
-        <x:v>485.64850159083625</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.876266859965487</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>752.0848839925635</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>483.3545081069395</x:v>
       </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2.29399348389677</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.004745985493921</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.004745985493920824</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc7077d425d54f5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59d391fcf37b4830"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4978,20 +4598,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4999,822 +4609,288 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>14419.1214755306</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.092120116566827</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1236.2893173520545</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>14419.1214755306</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1240.2647415795204</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$57,A2,'Species'!$U$2:$U$57))</x:f>
-        <x:v>17883527.970652673</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.092120116566827</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1236.2893173520545</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>17826205.845800072</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>57322.12485260144</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.003215609947986</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0032156099479860303</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>130.3539851943</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.650026251925707</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>446.71059378092417</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>130.3539851943</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>517.314544361435</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$57,A3,'Species'!$U$2:$U$57))</x:f>
-        <x:v>67434.01245648655</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.650026251925707</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>446.71059378092417</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>58230.50612785555</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>9203.506328631003</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.158053002466148</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.15805300246614806</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>421.5615797025</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.3536843331342507</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>225.779409643681</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>421.5615797025</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>361.57977877382126</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$57,A4,'Species'!$U$2:$U$57))</x:f>
-        <x:v>152428.14272837256</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.3536843331342507</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>225.779409643681</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>95179.92459368802</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>57248.21813468455</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.6014736655767539</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.6014736655767537</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>497.0017374107</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9444932468190803</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>880.0214274468676</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>497.0017374107</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>974.6521089387694</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$57,A5,'Species'!$U$2:$U$57))</x:f>
-        <x:v>484403.7915135712</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9444932468190803</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>880.0214274468676</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>437372.17839973746</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>47031.613113833766</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.107532246989083</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.10753224698908283</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2358.3315819802</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.9771930619983196</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>948.8401685631416</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2358.3315819802</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1689.3113151604098</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$57,A6,'Species'!$U$2:$U$57))</x:f>
-        <x:v>3983956.2263393016</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.9771930619983196</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>948.8401685631416</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2237679.7357738735</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1746276.490565428</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.7803960784233943</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.7803960784233943</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3302.7951952180006</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.328060087093245</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>212.84335064031274</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3302.7951952180006</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>747.9103576104962</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$57,A7,'Species'!$U$2:$U$57))</x:f>
-        <x:v>2470194.7355697234</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.328060087093245</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>212.84335064031274</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>702977.995828925</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1767216.7397407982</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>3.5139005064546343</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>2.513900506454634</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>51352.8863252675</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.380819465741164</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>240.33635249384852</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>51352.8863252675</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>240.9952084214277</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$57,A8,'Species'!$U$2:$U$57))</x:f>
-        <x:v>12375799.542999726</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.380819465741164</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>240.33635249384852</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>12341965.389446024</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>33834.15355370194</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0027413910577512</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0027413910577511837</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.0026092687000000003</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.53</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>33.88441561392024</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.0026092687000000003</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$57,A9,'Species'!$U$2:$U$57))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>0.08841354507919337</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.53</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>0.08841354507919337</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.04108159</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.75</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>562.341325190349</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.04108159</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>562.341325190349</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$57,A10,'Species'!$U$2:$U$57))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>23.101875761526593</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.75</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>562.341325190349</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>23.101875761526593</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>12.529248864200001</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>12.529248864200001</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>204.17379446695298</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$57,A11,'Species'!$U$2:$U$57))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2558.144282424475</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>2558.144282424475</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>455.664981087</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.0804629911946995</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>120.3546824067198</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>455.664981087</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>120.3975634053982</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$57,A12,'Species'!$U$2:$U$57))</x:f>
-        <x:v>54860.95345204166</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.0804629911946995</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>120.3546824067198</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>54841.41408258987</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>19.539369451784296</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.000356288578233</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.00035628857823320287</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>67877.848601801</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.01</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>102.32929922807536</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>67877.848601801</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$57,A13,'Species'!$U$2:$U$57))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>6945892.680531691</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.01</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>6945892.680531691</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>186.7963899036</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>186.7963899036</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$57,A14,'Species'!$U$2:$U$57))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>24064.03655512085</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>24064.03655512085</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>14217.770562943397</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.436763985704752</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>273.378266750053</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>14217.770562943397</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>299.95140915308235</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$57,A15,'Species'!$U$2:$U$57))</x:f>
-        <x:v>4264640.315370085</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.436763985704752</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>273.378266750053</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>3886829.473547391</x:v>
       </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>377810.8418226936</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0972028344423037</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.09720283444230372</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G15">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O15">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcaab4e54705459c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9ad94b358744644"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5989,7 +5065,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6088,7 +5164,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>48709783.74274053</x:v>
+        <x:v>44737293.36258347</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6102,7 +5178,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>48709783.74274052</x:v>
+        <x:v>44613820.51525869</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6116,7 +5192,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-3972490.3801570535</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6130,7 +5206,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-4095963.2274818346</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6141,9 +5217,9 @@
         <x:v>EEZ_616</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6155,47 +5231,19 @@
         <x:v>EEZ_616</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_616</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_616</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3f31b50749546c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50327c123b234648"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6242,7 +5290,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
